--- a/deliverables/PBCP-BH-05_rev4.xlsx
+++ b/deliverables/PBCP-BH-05_rev4.xlsx
@@ -12722,12 +12722,16 @@
         <v>39</v>
       </c>
       <c r="C14" s="8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="7"/>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GWL analisis likuefaksi (Report BP-00-GEO-RPT-003)</t>
+        </is>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="inlineStr">
@@ -12758,12 +12762,16 @@
         <v>43</v>
       </c>
       <c r="C16" s="8">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="7"/>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Report Tabel 5.1</t>
+        </is>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
@@ -12773,12 +12781,16 @@
         <v>46</v>
       </c>
       <c r="C17" s="8">
-        <v>18.399999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="7"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Report Tabel 5.1</t>
+        </is>
+      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
@@ -12932,7 +12944,11 @@
       <c r="D26" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E26" s="7"/>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sesuai perhitungan sebelumnya</t>
+        </is>
+      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
@@ -12945,7 +12961,11 @@
       <c r="D27" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E27" s="7"/>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sesuai perhitungan sebelumnya</t>
+        </is>
+      </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
@@ -13184,7 +13204,11 @@
       <c r="D45" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E45" s="7"/>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DD_max tidak difaktorkan (beban faktor 1,0)</t>
+        </is>
+      </c>
     </row>
     <row r="47" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
@@ -13203,12 +13227,16 @@
         <v>9</v>
       </c>
       <c r="C48" s="14">
-        <v>3000</v>
+        <v>5152.9</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E48" s="7"/>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GROUP WPD 2 cellar 4x1, ASD2(max) - beban lama, update dgn GROUP beban revisi</t>
+        </is>
+      </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
@@ -13218,12 +13246,16 @@
         <v>13</v>
       </c>
       <c r="C49" s="14">
-        <v>600</v>
+        <v>1583.9</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E49" s="7"/>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GROUP WPD 2 cellar 4x1, LRFD3 - beban lama, update dgn GROUP beban revisi</t>
+        </is>
+      </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
@@ -13233,12 +13265,16 @@
         <v>18</v>
       </c>
       <c r="C50" s="14">
-        <v>500</v>
+        <v>1101.5</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E50" s="7"/>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GROUP WPD 2 cellar 4x1, ASD1 (DL) - beban lama, update dgn GROUP beban revisi</t>
+        </is>
+      </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
@@ -13248,12 +13284,16 @@
         <v>103</v>
       </c>
       <c r="C51" s="14">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E51" s="7"/>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GROUP: tidak ada tiang tarik pada kombinasi yang ditinjau</t>
+        </is>
+      </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
@@ -13453,8 +13493,10 @@
       <c r="G7" s="11">
         <v>0</v>
       </c>
-      <c r="H7" s="6" t="s">
-        <v>123</v>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I7" s="16">
         <f>IF(F7="Clay",Input!$C$32*G7,0)</f>
@@ -13502,8 +13544,10 @@
       <c r="G8" s="11">
         <v>46</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>123</v>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I8" s="20">
         <f>IF(F8="Clay",Input!$C$32*G8,0)</f>
@@ -13553,8 +13597,10 @@
       <c r="G9" s="11">
         <v>50</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>123</v>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I9" s="16">
         <f>IF(F9="Clay",Input!$C$32*G9,0)</f>
@@ -13602,8 +13648,10 @@
       <c r="G10" s="11">
         <v>50</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>123</v>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I10" s="20">
         <f>IF(F10="Clay",Input!$C$32*G10,0)</f>
@@ -13653,8 +13701,10 @@
       <c r="G11" s="11">
         <v>32</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>123</v>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I11" s="16">
         <f>IF(F11="Clay",Input!$C$32*G11,0)</f>
@@ -13704,8 +13754,10 @@
       <c r="G12" s="11">
         <v>28</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>123</v>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I12" s="20">
         <f>IF(F12="Clay",Input!$C$32*G12,0)</f>
@@ -13755,8 +13807,10 @@
       <c r="G13" s="11">
         <v>35</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>123</v>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I13" s="16">
         <f>IF(F13="Clay",Input!$C$32*G13,0)</f>
@@ -13806,8 +13860,10 @@
       <c r="G14" s="11">
         <v>40</v>
       </c>
-      <c r="H14" s="6" t="s">
-        <v>123</v>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I14" s="20">
         <f>IF(F14="Clay",Input!$C$32*G14,0)</f>
@@ -13857,8 +13913,10 @@
       <c r="G15" s="11">
         <v>42</v>
       </c>
-      <c r="H15" s="6" t="s">
-        <v>123</v>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I15" s="16">
         <f>IF(F15="Clay",Input!$C$32*G15,0)</f>
@@ -13908,8 +13966,10 @@
       <c r="G16" s="11">
         <v>42</v>
       </c>
-      <c r="H16" s="6" t="s">
-        <v>123</v>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I16" s="20">
         <f>IF(F16="Clay",Input!$C$32*G16,0)</f>
@@ -13959,8 +14019,10 @@
       <c r="G17" s="11">
         <v>50</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>123</v>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I17" s="16">
         <f>IF(F17="Clay",Input!$C$32*G17,0)</f>
@@ -14008,8 +14070,10 @@
       <c r="G18" s="11">
         <v>30</v>
       </c>
-      <c r="H18" s="6" t="s">
-        <v>123</v>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L</t>
+        </is>
       </c>
       <c r="I18" s="20">
         <f>IF(F18="Clay",Input!$C$32*G18,0)</f>
@@ -14059,8 +14123,10 @@
       <c r="G19" s="11">
         <v>26</v>
       </c>
-      <c r="H19" s="6" t="s">
-        <v>123</v>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L</t>
+        </is>
       </c>
       <c r="I19" s="16">
         <f>IF(F19="Clay",Input!$C$32*G19,0)</f>
@@ -14110,8 +14176,10 @@
       <c r="G20" s="11">
         <v>41</v>
       </c>
-      <c r="H20" s="6" t="s">
-        <v>123</v>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I20" s="20">
         <f>IF(F20="Clay",Input!$C$32*G20,0)</f>
@@ -14161,8 +14229,10 @@
       <c r="G21" s="11">
         <v>40</v>
       </c>
-      <c r="H21" s="6" t="s">
-        <v>123</v>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I21" s="16">
         <f>IF(F21="Clay",Input!$C$32*G21,0)</f>
@@ -14212,8 +14282,10 @@
       <c r="G22" s="11">
         <v>50</v>
       </c>
-      <c r="H22" s="6" t="s">
-        <v>123</v>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I22" s="20">
         <f>IF(F22="Clay",Input!$C$32*G22,0)</f>
@@ -14261,8 +14333,10 @@
       <c r="G23" s="11">
         <v>40</v>
       </c>
-      <c r="H23" s="6" t="s">
-        <v>123</v>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I23" s="16">
         <f>IF(F23="Clay",Input!$C$32*G23,0)</f>
@@ -14310,8 +14384,10 @@
       <c r="G24" s="11">
         <v>21</v>
       </c>
-      <c r="H24" s="6" t="s">
-        <v>123</v>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I24" s="20">
         <f>IF(F24="Clay",Input!$C$32*G24,0)</f>
@@ -14331,7 +14407,11 @@
       <c r="N24" s="20">
         <f>IF(F24="Clay",Input!$C$35*I24,MIN(Input!$C$33*G24,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O24" s="21"/>
+      <c r="O24" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P24" s="11"/>
       <c r="Q24" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B24),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14359,8 +14439,10 @@
       <c r="G25" s="11">
         <v>31</v>
       </c>
-      <c r="H25" s="6" t="s">
-        <v>123</v>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I25" s="16">
         <f>IF(F25="Clay",Input!$C$32*G25,0)</f>
@@ -14380,7 +14462,11 @@
       <c r="N25" s="16">
         <f>IF(F25="Clay",Input!$C$35*I25,MIN(Input!$C$33*G25,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O25" s="17"/>
+      <c r="O25" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P25" s="11"/>
       <c r="Q25" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B25),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14408,8 +14494,10 @@
       <c r="G26" s="11">
         <v>50</v>
       </c>
-      <c r="H26" s="6" t="s">
-        <v>123</v>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I26" s="20">
         <f>IF(F26="Clay",Input!$C$32*G26,0)</f>
@@ -14429,7 +14517,11 @@
       <c r="N26" s="20">
         <f>IF(F26="Clay",Input!$C$35*I26,MIN(Input!$C$33*G26,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O26" s="21"/>
+      <c r="O26" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P26" s="11"/>
       <c r="Q26" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B26),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14457,8 +14549,10 @@
       <c r="G27" s="11">
         <v>40</v>
       </c>
-      <c r="H27" s="6" t="s">
-        <v>123</v>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I27" s="16">
         <f>IF(F27="Clay",Input!$C$32*G27,0)</f>
@@ -14478,7 +14572,11 @@
       <c r="N27" s="16">
         <f>IF(F27="Clay",Input!$C$35*I27,MIN(Input!$C$33*G27,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O27" s="17"/>
+      <c r="O27" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P27" s="11"/>
       <c r="Q27" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B27),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14506,8 +14604,10 @@
       <c r="G28" s="11">
         <v>43</v>
       </c>
-      <c r="H28" s="6" t="s">
-        <v>123</v>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I28" s="20">
         <f>IF(F28="Clay",Input!$C$32*G28,0)</f>
@@ -14527,7 +14627,11 @@
       <c r="N28" s="20">
         <f>IF(F28="Clay",Input!$C$35*I28,MIN(Input!$C$33*G28,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O28" s="21"/>
+      <c r="O28" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P28" s="11"/>
       <c r="Q28" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B28),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14555,8 +14659,10 @@
       <c r="G29" s="11">
         <v>26</v>
       </c>
-      <c r="H29" s="6" t="s">
-        <v>123</v>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I29" s="16">
         <f>IF(F29="Clay",Input!$C$32*G29,0)</f>
@@ -14576,7 +14682,11 @@
       <c r="N29" s="16">
         <f>IF(F29="Clay",Input!$C$35*I29,MIN(Input!$C$33*G29,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O29" s="17"/>
+      <c r="O29" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P29" s="11"/>
       <c r="Q29" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B29),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14602,10 +14712,12 @@
         <v>122</v>
       </c>
       <c r="G30" s="11">
-        <v>50</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>123</v>
+        <v>53</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I30" s="20">
         <f>IF(F30="Clay",Input!$C$32*G30,0)</f>
@@ -14625,7 +14737,11 @@
       <c r="N30" s="20">
         <f>IF(F30="Clay",Input!$C$35*I30,MIN(Input!$C$33*G30,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O30" s="21"/>
+      <c r="O30" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P30" s="11"/>
       <c r="Q30" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B30),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14651,10 +14767,12 @@
         <v>122</v>
       </c>
       <c r="G31" s="11">
-        <v>50</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>123</v>
+        <v>54</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I31" s="16">
         <f>IF(F31="Clay",Input!$C$32*G31,0)</f>
@@ -14674,7 +14792,11 @@
       <c r="N31" s="16">
         <f>IF(F31="Clay",Input!$C$35*I31,MIN(Input!$C$33*G31,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O31" s="17"/>
+      <c r="O31" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P31" s="11"/>
       <c r="Q31" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B31),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14702,8 +14824,10 @@
       <c r="G32" s="11">
         <v>50</v>
       </c>
-      <c r="H32" s="6" t="s">
-        <v>123</v>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I32" s="20">
         <f>IF(F32="Clay",Input!$C$32*G32,0)</f>
@@ -14723,7 +14847,11 @@
       <c r="N32" s="20">
         <f>IF(F32="Clay",Input!$C$35*I32,MIN(Input!$C$33*G32,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O32" s="21"/>
+      <c r="O32" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P32" s="11"/>
       <c r="Q32" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B32),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14751,8 +14879,10 @@
       <c r="G33" s="11">
         <v>50</v>
       </c>
-      <c r="H33" s="6" t="s">
-        <v>123</v>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I33" s="16">
         <f>IF(F33="Clay",Input!$C$32*G33,0)</f>
@@ -14772,7 +14902,11 @@
       <c r="N33" s="16">
         <f>IF(F33="Clay",Input!$C$35*I33,MIN(Input!$C$33*G33,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O33" s="17"/>
+      <c r="O33" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P33" s="11"/>
       <c r="Q33" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B33),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14800,8 +14934,10 @@
       <c r="G34" s="11">
         <v>37</v>
       </c>
-      <c r="H34" s="6" t="s">
-        <v>123</v>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I34" s="20">
         <f>IF(F34="Clay",Input!$C$32*G34,0)</f>
@@ -14821,7 +14957,11 @@
       <c r="N34" s="20">
         <f>IF(F34="Clay",Input!$C$35*I34,MIN(Input!$C$33*G34,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O34" s="21"/>
+      <c r="O34" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P34" s="11"/>
       <c r="Q34" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B34),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14849,8 +14989,10 @@
       <c r="G35" s="11">
         <v>50</v>
       </c>
-      <c r="H35" s="6" t="s">
-        <v>123</v>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I35" s="16">
         <f>IF(F35="Clay",Input!$C$32*G35,0)</f>
@@ -14870,7 +15012,11 @@
       <c r="N35" s="16">
         <f>IF(F35="Clay",Input!$C$35*I35,MIN(Input!$C$33*G35,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O35" s="17"/>
+      <c r="O35" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P35" s="11"/>
       <c r="Q35" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B35),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14898,8 +15044,10 @@
       <c r="G36" s="11">
         <v>50</v>
       </c>
-      <c r="H36" s="6" t="s">
-        <v>123</v>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I36" s="20">
         <f>IF(F36="Clay",Input!$C$32*G36,0)</f>
@@ -14919,7 +15067,11 @@
       <c r="N36" s="20">
         <f>IF(F36="Clay",Input!$C$35*I36,MIN(Input!$C$33*G36,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O36" s="21"/>
+      <c r="O36" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P36" s="11"/>
       <c r="Q36" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B36),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14947,8 +15099,10 @@
       <c r="G37" s="11">
         <v>50</v>
       </c>
-      <c r="H37" s="6" t="s">
-        <v>123</v>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I37" s="16">
         <f>IF(F37="Clay",Input!$C$32*G37,0)</f>
@@ -14968,7 +15122,11 @@
       <c r="N37" s="16">
         <f>IF(F37="Clay",Input!$C$35*I37,MIN(Input!$C$33*G37,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O37" s="17"/>
+      <c r="O37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P37" s="11"/>
       <c r="Q37" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B37),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14996,8 +15154,10 @@
       <c r="G38" s="11">
         <v>50</v>
       </c>
-      <c r="H38" s="6" t="s">
-        <v>123</v>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I38" s="20">
         <f>IF(F38="Clay",Input!$C$32*G38,0)</f>
@@ -15017,7 +15177,11 @@
       <c r="N38" s="20">
         <f>IF(F38="Clay",Input!$C$35*I38,MIN(Input!$C$33*G38,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O38" s="21"/>
+      <c r="O38" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P38" s="11"/>
       <c r="Q38" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B38),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15045,8 +15209,10 @@
       <c r="G39" s="11">
         <v>27</v>
       </c>
-      <c r="H39" s="6" t="s">
-        <v>123</v>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I39" s="16">
         <f>IF(F39="Clay",Input!$C$32*G39,0)</f>
@@ -15066,7 +15232,11 @@
       <c r="N39" s="16">
         <f>IF(F39="Clay",Input!$C$35*I39,MIN(Input!$C$33*G39,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O39" s="17"/>
+      <c r="O39" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P39" s="11"/>
       <c r="Q39" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B39),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15094,8 +15264,10 @@
       <c r="G40" s="11">
         <v>25</v>
       </c>
-      <c r="H40" s="6" t="s">
-        <v>123</v>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I40" s="20">
         <f>IF(F40="Clay",Input!$C$32*G40,0)</f>
@@ -15115,7 +15287,11 @@
       <c r="N40" s="20">
         <f>IF(F40="Clay",Input!$C$35*I40,MIN(Input!$C$33*G40,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O40" s="21"/>
+      <c r="O40" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P40" s="11"/>
       <c r="Q40" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B40),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15143,8 +15319,10 @@
       <c r="G41" s="11">
         <v>29</v>
       </c>
-      <c r="H41" s="6" t="s">
-        <v>123</v>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I41" s="16">
         <f>IF(F41="Clay",Input!$C$32*G41,0)</f>
@@ -15164,7 +15342,11 @@
       <c r="N41" s="16">
         <f>IF(F41="Clay",Input!$C$35*I41,MIN(Input!$C$33*G41,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O41" s="17"/>
+      <c r="O41" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P41" s="11"/>
       <c r="Q41" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B41),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15192,8 +15374,10 @@
       <c r="G42" s="11">
         <v>35</v>
       </c>
-      <c r="H42" s="6" t="s">
-        <v>123</v>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I42" s="20">
         <f>IF(F42="Clay",Input!$C$32*G42,0)</f>
@@ -15213,7 +15397,11 @@
       <c r="N42" s="20">
         <f>IF(F42="Clay",Input!$C$35*I42,MIN(Input!$C$33*G42,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O42" s="21"/>
+      <c r="O42" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P42" s="11"/>
       <c r="Q42" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B42),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15241,8 +15429,10 @@
       <c r="G43" s="11">
         <v>50</v>
       </c>
-      <c r="H43" s="6" t="s">
-        <v>123</v>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I43" s="16">
         <f>IF(F43="Clay",Input!$C$32*G43,0)</f>
@@ -15262,7 +15452,11 @@
       <c r="N43" s="16">
         <f>IF(F43="Clay",Input!$C$35*I43,MIN(Input!$C$33*G43,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O43" s="17"/>
+      <c r="O43" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P43" s="11"/>
       <c r="Q43" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B43),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15290,8 +15484,10 @@
       <c r="G44" s="11">
         <v>50</v>
       </c>
-      <c r="H44" s="6" t="s">
-        <v>123</v>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I44" s="20">
         <f>IF(F44="Clay",Input!$C$32*G44,0)</f>
@@ -15311,7 +15507,11 @@
       <c r="N44" s="20">
         <f>IF(F44="Clay",Input!$C$35*I44,MIN(Input!$C$33*G44,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O44" s="21"/>
+      <c r="O44" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P44" s="11"/>
       <c r="Q44" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B44),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15339,8 +15539,10 @@
       <c r="G45" s="11">
         <v>50</v>
       </c>
-      <c r="H45" s="6" t="s">
-        <v>123</v>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I45" s="16">
         <f>IF(F45="Clay",Input!$C$32*G45,0)</f>
@@ -15360,7 +15562,11 @@
       <c r="N45" s="16">
         <f>IF(F45="Clay",Input!$C$35*I45,MIN(Input!$C$33*G45,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O45" s="17"/>
+      <c r="O45" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P45" s="11"/>
       <c r="Q45" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B45),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15388,8 +15594,10 @@
       <c r="G46" s="11">
         <v>29</v>
       </c>
-      <c r="H46" s="6" t="s">
-        <v>123</v>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I46" s="20">
         <f>IF(F46="Clay",Input!$C$32*G46,0)</f>
@@ -15409,7 +15617,11 @@
       <c r="N46" s="20">
         <f>IF(F46="Clay",Input!$C$35*I46,MIN(Input!$C$33*G46,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O46" s="21"/>
+      <c r="O46" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P46" s="11"/>
       <c r="Q46" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B46),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15437,8 +15649,10 @@
       <c r="G47" s="11">
         <v>44</v>
       </c>
-      <c r="H47" s="6" t="s">
-        <v>123</v>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I47" s="16">
         <f>IF(F47="Clay",Input!$C$32*G47,0)</f>
@@ -15458,7 +15672,11 @@
       <c r="N47" s="16">
         <f>IF(F47="Clay",Input!$C$35*I47,MIN(Input!$C$33*G47,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O47" s="17"/>
+      <c r="O47" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 25 m)</t>
+        </is>
+      </c>
       <c r="P47" s="11"/>
       <c r="Q47" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B47),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>

--- a/deliverables/PBCP-BH-05_rev4.xlsx
+++ b/deliverables/PBCP-BH-05_rev4.xlsx
@@ -13227,14 +13227,14 @@
         <v>9</v>
       </c>
       <c r="C48" s="14">
-        <v>5152.9</v>
+        <v>3000.0</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GROUP WPD 2 cellar 4x1, ASD2(max) - beban lama, update dgn GROUP beban revisi</t>
+          <t xml:space="preserve">beban seragam semua BH (sama dengan BH-03) - update dgn GROUP beban revisi</t>
         </is>
       </c>
     </row>
@@ -13246,14 +13246,14 @@
         <v>13</v>
       </c>
       <c r="C49" s="14">
-        <v>1583.9</v>
+        <v>600.0</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GROUP WPD 2 cellar 4x1, LRFD3 - beban lama, update dgn GROUP beban revisi</t>
+          <t xml:space="preserve">beban seragam semua BH (sama dengan BH-03) - update dgn GROUP beban revisi</t>
         </is>
       </c>
     </row>
@@ -13265,14 +13265,14 @@
         <v>18</v>
       </c>
       <c r="C50" s="14">
-        <v>1101.5</v>
+        <v>500.0</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GROUP WPD 2 cellar 4x1, ASD1 (DL) - beban lama, update dgn GROUP beban revisi</t>
+          <t xml:space="preserve">beban seragam semua BH (sama dengan BH-03) - update dgn GROUP beban revisi</t>
         </is>
       </c>
     </row>
@@ -13291,7 +13291,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GROUP: tidak ada tiang tarik pada kombinasi yang ditinjau</t>
+          <t xml:space="preserve">tidak ada tiang tarik pada kombinasi yang ditinjau</t>
         </is>
       </c>
     </row>
